--- a/data/exports/MFAS_Workbook_Tab_Map.xlsx
+++ b/data/exports/MFAS_Workbook_Tab_Map.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>

--- a/data/exports/MFAS_Workbook_Tab_Map.xlsx
+++ b/data/exports/MFAS_Workbook_Tab_Map.xlsx
@@ -588,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB21"/>
+  <dimension ref="A1:BB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3362,48 +3362,143 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Issues Log.xlsx</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>The master issues list for the initiative.</t>
-        </is>
-      </c>
+          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model_v2.xlsx</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>Risk model</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Hillsborough</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>FY27–FY27</t>
+          <t>FY18–FY35</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>282</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Sheet1 (5)</t>
+          <t>Sheet1 (46)</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0 Executive Dashboard (14)</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1 Budget Waterfall (11)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2 Policy Shifts (8)</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>3 Structural Health (14)</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>4 Cost Allocation Stress (17)</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>5 Personnel Exposure (21)</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>6 Fire Station Bridge (11)</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>7 Ridgewalk Bridge (8)</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>8 Rail Station Bridge (7)</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>9 Affordable Housing Bridge (11)</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>10 Vehicle Replacement (8)</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>11 Debt Service Build-up (14)</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>12 Tax Equivalent Exposure (10)</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>13 FY29 Fiscal Cliff (9)</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>14 Base Case (18)</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15 Optimistic Case (18)</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>16 Conservative Case (18)</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17 Questions for Management (9)</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>18 Sources &amp; Assumptions (10)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OC Design.xlsx</t>
+          <t>Issues Log.xlsx</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Early design notes for the Orange County side.</t>
+          <t>The master issues list for the initiative.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3413,23 +3508,59 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Orange County</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>FY25–FY25</t>
+          <t>FY27–FY27</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Sheet1 (5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>OC Design.xlsx</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Early design notes for the Orange County side.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Orange County</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>FY25–FY25</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
         <v>134</v>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Sheet1 (134)</t>
         </is>
@@ -3446,7 +3577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F350"/>
+  <dimension ref="A1:F370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -13064,43 +13195,523 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Issues Log.xlsx</t>
+          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model_v2.xlsx</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>Risk model</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
       <c r="E349" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="F349" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>0 Executive Dashboard</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>OC Design.xlsx</t>
+          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model_v2.xlsx</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>Risk model</t>
         </is>
       </c>
       <c r="D350" t="inlineStr"/>
       <c r="E350" t="n">
+        <v>14</v>
+      </c>
+      <c r="F350" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>1 Budget Waterfall</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model_v2.xlsx</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Risk model</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="n">
+        <v>11</v>
+      </c>
+      <c r="F351" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2 Policy Shifts</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model_v2.xlsx</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Risk model</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="n">
+        <v>8</v>
+      </c>
+      <c r="F352" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>3 Structural Health</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model_v2.xlsx</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Risk model</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="n">
+        <v>14</v>
+      </c>
+      <c r="F353" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>4 Cost Allocation Stress</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model_v2.xlsx</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Risk model</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="n">
+        <v>17</v>
+      </c>
+      <c r="F354" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>5 Personnel Exposure</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model_v2.xlsx</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Risk model</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" t="n">
+        <v>21</v>
+      </c>
+      <c r="F355" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>6 Fire Station Bridge</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model_v2.xlsx</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Risk model</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" t="n">
+        <v>11</v>
+      </c>
+      <c r="F356" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>7 Ridgewalk Bridge</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model_v2.xlsx</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Risk model</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="n">
+        <v>8</v>
+      </c>
+      <c r="F357" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>8 Rail Station Bridge</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model_v2.xlsx</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Risk model</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" t="n">
+        <v>7</v>
+      </c>
+      <c r="F358" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>9 Affordable Housing Bridge</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model_v2.xlsx</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Risk model</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="n">
+        <v>11</v>
+      </c>
+      <c r="F359" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>10 Vehicle Replacement</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model_v2.xlsx</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Risk model</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" t="n">
+        <v>8</v>
+      </c>
+      <c r="F360" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>11 Debt Service Build-up</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model_v2.xlsx</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Risk model</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr"/>
+      <c r="E361" t="n">
+        <v>14</v>
+      </c>
+      <c r="F361" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>12 Tax Equivalent Exposure</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model_v2.xlsx</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Risk model</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr"/>
+      <c r="E362" t="n">
+        <v>10</v>
+      </c>
+      <c r="F362" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>13 FY29 Fiscal Cliff</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model_v2.xlsx</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Risk model</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr"/>
+      <c r="E363" t="n">
+        <v>9</v>
+      </c>
+      <c r="F363" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>14 Base Case</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model_v2.xlsx</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Risk model</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr"/>
+      <c r="E364" t="n">
+        <v>18</v>
+      </c>
+      <c r="F364" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>15 Optimistic Case</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model_v2.xlsx</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Risk model</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr"/>
+      <c r="E365" t="n">
+        <v>18</v>
+      </c>
+      <c r="F365" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>16 Conservative Case</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model_v2.xlsx</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Risk model</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr"/>
+      <c r="E366" t="n">
+        <v>18</v>
+      </c>
+      <c r="F366" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>17 Questions for Management</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model_v2.xlsx</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Risk model</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr"/>
+      <c r="E367" t="n">
+        <v>9</v>
+      </c>
+      <c r="F367" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>18 Sources &amp; Assumptions</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model_v2.xlsx</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Risk model</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr"/>
+      <c r="E368" t="n">
+        <v>10</v>
+      </c>
+      <c r="F368" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Issues Log.xlsx</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr"/>
+      <c r="E369" t="n">
+        <v>5</v>
+      </c>
+      <c r="F369" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>OC Design.xlsx</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="n">
         <v>134</v>
       </c>
-      <c r="F350" t="n">
+      <c r="F370" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13213,11 +13824,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Change_Log</t>
+          <t>Sheet1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -13228,7 +13839,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data_Dictionary</t>
+          <t>Change_Log</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -13243,7 +13854,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data_Quality_Gaps</t>
+          <t>Data_Dictionary</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -13258,7 +13869,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dim_Fiscal_Year</t>
+          <t>Data_Quality_Gaps</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -13273,7 +13884,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dim_Fund</t>
+          <t>Dim_Fiscal_Year</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -13288,7 +13899,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fact_GF_BudgetActual_2025</t>
+          <t>Dim_Fund</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -13303,7 +13914,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Fact_GF_BudgetActual_2025</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -13318,7 +13929,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -13828,7 +14439,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Affordable_Housing_Rampup</t>
+          <t>0 Executive Dashboard</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -13843,7 +14454,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Capital_Project_Bridges</t>
+          <t>1 Budget Waterfall</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -13858,7 +14469,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cost_Allocation_Risk</t>
+          <t>10 Vehicle Replacement</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -13873,7 +14484,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Debt_Growth_Drivers</t>
+          <t>11 Debt Service Build-up</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -13888,7 +14499,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Dim_Fiscal_Years</t>
+          <t>12 Tax Equivalent Exposure</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -13903,7 +14514,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Document_Control</t>
+          <t>13 FY29 Fiscal Cliff</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -13918,7 +14529,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Fact_Affordable_Housing</t>
+          <t>14 Base Case</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -13933,7 +14544,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Fact_Annual_GF</t>
+          <t>15 Optimistic Case</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -13948,7 +14559,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Fact_Budget_Category</t>
+          <t>16 Conservative Case</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -13963,7 +14574,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Fact_Debt_Service</t>
+          <t>17 Questions for Management</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -13978,7 +14589,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Fact_Expense_Function</t>
+          <t>18 Sources &amp; Assumptions</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -13993,7 +14604,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Fact_Expense_GF_Hist</t>
+          <t>2 Policy Shifts</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -14008,7 +14619,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Fact_Expense_Type</t>
+          <t>3 Structural Health</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -14023,7 +14634,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Fact_GF_BudgetActual_Hist</t>
+          <t>4 Cost Allocation Stress</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -14038,7 +14649,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Fact_GF_Summary_Hist</t>
+          <t>5 Personnel Exposure</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -14053,7 +14664,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Fact_Revenue_GF</t>
+          <t>6 Fire Station Bridge</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -14068,7 +14679,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Fact_Revenue_GF_Hist</t>
+          <t>7 Ridgewalk Bridge</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -14083,7 +14694,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Fact_Staffing_Payroll</t>
+          <t>8 Rail Station Bridge</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -14098,7 +14709,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Fact_Stormwater</t>
+          <t>9 Affordable Housing Bridge</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -14113,7 +14724,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Fact_Utility_Rate_Study</t>
+          <t>Affordable_Housing_Rampup</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -14128,7 +14739,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Function_Descriptions</t>
+          <t>Capital_Project_Bridges</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -14143,7 +14754,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GF_Gross_to_Net_Bridge</t>
+          <t>Cost_Allocation_Risk</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -14158,7 +14769,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Review_Dashboard_v2.0</t>
+          <t>Debt_Growth_Drivers</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -14173,7 +14784,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>v4_Sources_Assumptions</t>
+          <t>Dim_Fiscal_Years</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -14188,292 +14799,292 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0 Executive Dashboard</t>
+          <t>Document_Control</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Appears once — dead end or unfinished</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1 Budget Waterfall</t>
+          <t>Fact_Affordable_Housing</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Appears once — dead end or unfinished</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1. Staffing &amp; Compensation</t>
+          <t>Fact_Annual_GF</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Appears once — dead end or unfinished</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1.0 Fact_GF_Summary_Hist</t>
+          <t>Fact_Budget_Category</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Appears once — dead end or unfinished</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10 Vehicle Replacement</t>
+          <t>Fact_Debt_Service</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Appears once — dead end or unfinished</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10. Fact_Debt_Capital_2025</t>
+          <t>Fact_Expense_Function</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Appears once — dead end or unfinished</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>11 Debt Service Build-up</t>
+          <t>Fact_Expense_GF_Hist</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Appears once — dead end or unfinished</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>11. Fact_Enterprise_Funds_2025</t>
+          <t>Fact_Expense_Type</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Appears once — dead end or unfinished</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>12 Tax Equivalent Exposure</t>
+          <t>Fact_GF_BudgetActual_Hist</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Appears once — dead end or unfinished</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>12. Fact_FY26_Outlook</t>
+          <t>Fact_GF_Summary_Hist</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Appears once — dead end or unfinished</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>13 FY29 Fiscal Cliff</t>
+          <t>Fact_Revenue_GF</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Appears once — dead end or unfinished</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>13. Fact_Schools_2025</t>
+          <t>Fact_Revenue_GF_Hist</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Appears once — dead end or unfinished</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>14 Base Case</t>
+          <t>Fact_Staffing_Payroll</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Appears once — dead end or unfinished</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>15 Optimistic Case</t>
+          <t>Fact_Stormwater</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Appears once — dead end or unfinished</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>16 Conservative Case</t>
+          <t>Fact_Utility_Rate_Study</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Appears once — dead end or unfinished</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>17 Questions for Management</t>
+          <t>Function_Descriptions</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Appears once — dead end or unfinished</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>18 Sources &amp; Assumptions</t>
+          <t>GF_Gross_to_Net_Bridge</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Appears once — dead end or unfinished</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2 Policy Shifts</t>
+          <t>Review_Dashboard_v2.0</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Appears once — dead end or unfinished</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2. Utilities</t>
+          <t>v4_Sources_Assumptions</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Appears once — dead end or unfinished</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2.0 Fact_GF_BudgetActual_Hist</t>
+          <t>1. Staffing &amp; Compensation</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -14488,7 +15099,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3 Structural Health</t>
+          <t>1.0 Fact_GF_Summary_Hist</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -14503,7 +15114,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3. Capital Projects</t>
+          <t>10. Fact_Debt_Capital_2025</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -14518,7 +15129,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3.0 Fact_Revenue_GF_Hist</t>
+          <t>11. Fact_Enterprise_Funds_2025</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -14533,7 +15144,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4 Cost Allocation Stress</t>
+          <t>12. Fact_FY26_Outlook</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -14548,7 +15159,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4. Debt</t>
+          <t>13. Fact_Schools_2025</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -14563,7 +15174,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4.0 Fact_Expense_GF_Hist</t>
+          <t>2. Utilities</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -14578,7 +15189,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5 Personnel Exposure</t>
+          <t>2.0 Fact_GF_BudgetActual_Hist</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -14593,7 +15204,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5. Revenue &amp; Taxes</t>
+          <t>3. Capital Projects</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -14608,7 +15219,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5.0 Fact_Gov_Funds_Balance</t>
+          <t>3.0 Fact_Revenue_GF_Hist</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -14623,7 +15234,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>6 Fire Station Bridge</t>
+          <t>4. Debt</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -14638,7 +15249,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>6. Affordable Housing</t>
+          <t>4.0 Fact_Expense_GF_Hist</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -14653,7 +15264,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>6.0 Fact_Gov_Funds_Change</t>
+          <t>5. Revenue &amp; Taxes</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -14668,7 +15279,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>7 Ridgewalk Bridge</t>
+          <t>5.0 Fact_Gov_Funds_Balance</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -14683,7 +15294,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>7.0 Fact_Fund_Balance_2025</t>
+          <t>6. Affordable Housing</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -14698,7 +15309,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8 Rail Station Bridge</t>
+          <t>6.0 Fact_Gov_Funds_Change</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -14713,7 +15324,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>8.0 Fact_Net_Position_2025</t>
+          <t>7.0 Fact_Fund_Balance_2025</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -14728,7 +15339,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>9 Affordable Housing Bridge</t>
+          <t>8.0 Fact_Net_Position_2025</t>
         </is>
       </c>
       <c r="B108" t="n">

--- a/data/exports/MFAS_Workbook_Tab_Map.xlsx
+++ b/data/exports/MFAS_Workbook_Tab_Map.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>

--- a/data/exports/MFAS_Workbook_Tab_Map.xlsx
+++ b/data/exports/MFAS_Workbook_Tab_Map.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>source-set 655366136851</t>
         </is>
       </c>
     </row>

--- a/data/exports/MFAS_Workbook_Tab_Map.xlsx
+++ b/data/exports/MFAS_Workbook_Tab_Map.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>source-set 655366136851</t>
+          <t>source-set 8a8a25fe15f9</t>
         </is>
       </c>
     </row>

--- a/data/exports/MFAS_Workbook_Tab_Map.xlsx
+++ b/data/exports/MFAS_Workbook_Tab_Map.xlsx
@@ -30,6 +30,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
@@ -40,7 +41,7 @@
     </font>
     <font>
       <i val="1"/>
-      <color rgb="00555555"/>
+      <color rgb="006F6E6A"/>
       <sz val="9"/>
     </font>
     <font>
@@ -61,12 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="000B0B0B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8EDF5"/>
+        <fgColor rgb="00E4EEFA"/>
       </patternFill>
     </fill>
   </fills>
@@ -459,6 +460,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002A78D6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -579,12 +581,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 &amp;K6F6E6AMFAS · Orange County Efficiency &amp;&amp; Accountability Initiative&amp;R&amp;8 &amp;K6F6E6APage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000B0B0B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -3568,12 +3579,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 &amp;K6F6E6AMFAS · Orange County Efficiency &amp;&amp; Accountability Initiative&amp;R&amp;8 &amp;K6F6E6APage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000B0B0B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -13720,12 +13740,21 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 &amp;K6F6E6AMFAS · Orange County Efficiency &amp;&amp; Accountability Initiative&amp;R&amp;8 &amp;K6F6E6APage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000B0B0B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -16421,12 +16450,21 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 &amp;K6F6E6AMFAS · Orange County Efficiency &amp;&amp; Accountability Initiative&amp;R&amp;8 &amp;K6F6E6APage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000B0B0B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -16715,5 +16753,13 @@
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 &amp;K6F6E6AMFAS · Orange County Efficiency &amp;&amp; Accountability Initiative&amp;R&amp;8 &amp;K6F6E6APage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>